--- a/2025-MLS-projections/BSIA Catch/Use 2020 Proportion by Group/2025-2027 Catch by Scenario Using 2020.xlsx
+++ b/2025-MLS-projections/BSIA Catch/Use 2020 Proportion by Group/2025-2027 Catch by Scenario Using 2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jon.brodziak\Desktop\2024 WCNPO MLS Rebuilding\2025 MLS projections\BSIA Catch\Use 2020 Proportion by Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EC4952-60EC-40A0-81AF-CC6DAE0D6159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534AC5A5-1F2B-4521-9288-03468DAAF7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="326" windowWidth="13766" windowHeight="8185" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8863" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenario1-catch" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="135">
   <si>
     <t>Yr</t>
   </si>
@@ -435,6 +435,15 @@
   <si>
     <t>Scenario 3. MLS Catch (mt) by Fleet Group, 2025-2027</t>
   </si>
+  <si>
+    <t>Scenario 1. No Carryover Catch</t>
+  </si>
+  <si>
+    <t>Scenario 2. Carryover Catch in 2025</t>
+  </si>
+  <si>
+    <t>Scenario 3. Carryover Catch in 2025-2026</t>
+  </si>
 </sst>
 </file>
 
@@ -445,7 +454,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,6 +606,14 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1083,7 +1100,9 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1135,7 +1154,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1261,7 +1280,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
@@ -1269,9 +1287,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1339,6 +1354,14 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -2078,23 +2101,25 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18.899999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="23"/>
+    <row r="2" spans="1:18" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="73" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="44.15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="74" t="s">
+      <c r="E3" s="72" t="s">
         <v>113</v>
       </c>
       <c r="G3" s="30" t="s">
@@ -2141,7 +2166,7 @@
       <c r="B4" s="11">
         <v>1454.4</v>
       </c>
-      <c r="C4" s="49">
+      <c r="C4" s="48">
         <v>1454.4</v>
       </c>
       <c r="D4" s="13">
@@ -2200,7 +2225,7 @@
       <c r="B5" s="14">
         <v>358.4</v>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="49">
         <v>358.4</v>
       </c>
       <c r="D5" s="16">
@@ -2259,7 +2284,7 @@
       <c r="B6" s="14">
         <v>214.8</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="49">
         <v>214.8</v>
       </c>
       <c r="D6" s="16">
@@ -2318,7 +2343,7 @@
       <c r="B7" s="14">
         <v>228.4</v>
       </c>
-      <c r="C7" s="50">
+      <c r="C7" s="49">
         <v>228.4</v>
       </c>
       <c r="D7" s="16">
@@ -2377,7 +2402,7 @@
       <c r="B8" s="14">
         <v>68.8</v>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="49">
         <v>68.8</v>
       </c>
       <c r="D8" s="16">
@@ -2429,14 +2454,14 @@
         <v>190.96275638160924</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
         <v>109</v>
       </c>
       <c r="B9" s="14">
         <v>75.2</v>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="49">
         <v>75.2</v>
       </c>
       <c r="D9" s="16">
@@ -2489,19 +2514,19 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="20">
         <v>2400</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="75">
         <v>2400</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="22">
         <v>2400</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="22" t="s">
         <v>116</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -2807,23 +2832,25 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18.899999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="23"/>
+    <row r="2" spans="1:18" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="73" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="44.15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="74" t="s">
+      <c r="E3" s="72" t="s">
         <v>113</v>
       </c>
       <c r="G3" s="30" t="s">
@@ -2874,7 +2901,7 @@
       <c r="C4" s="12">
         <v>1454.4</v>
       </c>
-      <c r="D4" s="49">
+      <c r="D4" s="48">
         <v>1454.4</v>
       </c>
       <c r="E4" s="13" t="s">
@@ -2934,7 +2961,7 @@
       <c r="C5" s="15">
         <v>358.4</v>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="49">
         <v>358.4</v>
       </c>
       <c r="E5" s="16" t="s">
@@ -2994,7 +3021,7 @@
       <c r="C6" s="15">
         <v>214.8</v>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="49">
         <v>214.8</v>
       </c>
       <c r="E6" s="16" t="s">
@@ -3054,7 +3081,7 @@
       <c r="C7" s="15">
         <v>228.4</v>
       </c>
-      <c r="D7" s="50">
+      <c r="D7" s="49">
         <v>228.4</v>
       </c>
       <c r="E7" s="16" t="s">
@@ -3114,7 +3141,7 @@
       <c r="C8" s="15">
         <v>68.8</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="49">
         <v>68.8</v>
       </c>
       <c r="E8" s="16" t="s">
@@ -3163,7 +3190,7 @@
         <v>190.96275638160924</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
         <v>109</v>
       </c>
@@ -3173,7 +3200,7 @@
       <c r="C9" s="15">
         <v>75.2</v>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="49">
         <v>75.2</v>
       </c>
       <c r="E9" s="16" t="s">
@@ -3223,19 +3250,19 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="74">
         <v>3225</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="21">
         <v>2400</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="75">
         <v>2400</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="22" t="s">
         <v>116</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -3453,23 +3480,25 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18.899999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="23"/>
+    <row r="2" spans="1:18" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="73" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="44.15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="74" t="s">
+      <c r="E3" s="72" t="s">
         <v>113</v>
       </c>
       <c r="G3" s="30" t="s">
@@ -3513,7 +3542,7 @@
       <c r="A4" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="46">
+      <c r="B4" s="45">
         <f>1454.4 + 165</f>
         <v>1619.4</v>
       </c>
@@ -3574,7 +3603,7 @@
       <c r="A5" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="46">
         <f>358.4 + 165</f>
         <v>523.4</v>
       </c>
@@ -3635,7 +3664,7 @@
       <c r="A6" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="46">
         <f>214.8 + 165</f>
         <v>379.8</v>
       </c>
@@ -3696,7 +3725,7 @@
       <c r="A7" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="46">
         <f>228.4 + 165</f>
         <v>393.4</v>
       </c>
@@ -3757,7 +3786,7 @@
       <c r="A8" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="46">
         <f>68.8 + 165</f>
         <v>233.8</v>
       </c>
@@ -3814,11 +3843,11 @@
         <v>190.96275638160924</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="46">
         <v>75.2</v>
       </c>
       <c r="C9" s="44">
@@ -3874,19 +3903,19 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="48">
+      <c r="B10" s="76">
         <v>3225</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="74">
         <v>3225</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="22">
         <v>2400</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="22" t="s">
         <v>116</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -4127,17 +4156,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="20.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="I1" s="66" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="I1" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="68"/>
-      <c r="K1" s="67"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="65"/>
       <c r="M1" s="6" t="s">
         <v>90</v>
       </c>
@@ -4373,34 +4402,34 @@
       <c r="BR5" s="1"/>
     </row>
     <row r="6" spans="1:71" s="7" customFormat="1" ht="87.9" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="G6" s="54" t="s">
+      <c r="G6" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="53" t="s">
+      <c r="J6" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="54" t="s">
+      <c r="K6" s="52" t="s">
         <v>92</v>
       </c>
       <c r="M6" s="8" t="s">
@@ -4564,28 +4593,28 @@
       </c>
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.4">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="64">
+      <c r="B7" s="62">
         <f>SUM($K7:$K9)</f>
         <v>346.17200000000003</v>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="67">
         <f>B7/B$16</f>
         <v>0.2169634028469607</v>
       </c>
-      <c r="D7" s="55">
-        <v>0</v>
-      </c>
-      <c r="E7" s="62">
+      <c r="D7" s="53">
+        <v>0</v>
+      </c>
+      <c r="E7" s="60">
         <v>0</v>
       </c>
       <c r="F7" s="24">
         <f>SUM($K7:$K9)</f>
         <v>346.17200000000003</v>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="54">
         <f>F7/F$16</f>
         <v>0.14353550217788588</v>
       </c>
@@ -4774,14 +4803,14 @@
       </c>
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.4">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="65">
+      <c r="B8" s="63">
         <f>SUM($K10:$K12)</f>
         <v>137.2099</v>
       </c>
-      <c r="C8" s="70">
+      <c r="C8" s="68">
         <f t="shared" ref="C8:E16" si="0">B8/B$16</f>
         <v>8.5996345193404405E-2</v>
       </c>
@@ -4795,7 +4824,7 @@
         <f>SUM($K10:$K12)</f>
         <v>137.2099</v>
       </c>
-      <c r="G8" s="57">
+      <c r="G8" s="55">
         <f t="shared" ref="G8:G16" si="1">F8/F$16</f>
         <v>5.6892215142407547E-2</v>
       </c>
@@ -5008,14 +5037,14 @@
       </c>
     </row>
     <row r="9" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="65">
+      <c r="B9" s="63">
         <f>SUM($K13:$K16)</f>
         <v>597.90244000000007</v>
       </c>
-      <c r="C9" s="70">
+      <c r="C9" s="68">
         <f t="shared" si="0"/>
         <v>0.37473553017835282</v>
       </c>
@@ -5029,7 +5058,7 @@
         <f>SUM($K13:$K17)</f>
         <v>716.90244000000007</v>
       </c>
-      <c r="G9" s="57">
+      <c r="G9" s="55">
         <f t="shared" si="1"/>
         <v>0.29725382682005397</v>
       </c>
@@ -5242,14 +5271,14 @@
       </c>
     </row>
     <row r="10" spans="1:71" x14ac:dyDescent="0.4">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="65">
+      <c r="B10" s="63">
         <f>SUM($K18:$K21)</f>
         <v>63.744059999999998</v>
       </c>
-      <c r="C10" s="70">
+      <c r="C10" s="68">
         <f t="shared" si="0"/>
         <v>3.9951608359084012E-2</v>
       </c>
@@ -5263,7 +5292,7 @@
         <f>SUM($K18:$K21)</f>
         <v>63.744059999999998</v>
       </c>
-      <c r="G10" s="57">
+      <c r="G10" s="55">
         <f t="shared" si="1"/>
         <v>2.6430605776773652E-2</v>
       </c>
@@ -5476,14 +5505,14 @@
       </c>
     </row>
     <row r="11" spans="1:71" x14ac:dyDescent="0.4">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="65">
+      <c r="B11" s="63">
         <f>SUM($K22:$K24)</f>
         <v>209.49336000000002</v>
       </c>
-      <c r="C11" s="70">
+      <c r="C11" s="68">
         <f t="shared" si="0"/>
         <v>0.13130002501485782</v>
       </c>
@@ -5497,7 +5526,7 @@
         <f>SUM($K22:$K24)</f>
         <v>209.49336000000002</v>
       </c>
-      <c r="G11" s="57">
+      <c r="G11" s="55">
         <f t="shared" si="1"/>
         <v>8.6863566754482271E-2</v>
       </c>
@@ -5710,14 +5739,14 @@
       </c>
     </row>
     <row r="12" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="65">
+      <c r="B12" s="63">
         <f>SUM($K25)</f>
         <v>93.68</v>
       </c>
-      <c r="C12" s="70">
+      <c r="C12" s="68">
         <f t="shared" si="0"/>
         <v>5.8713967561510691E-2</v>
       </c>
@@ -5731,7 +5760,7 @@
         <f>SUM($K25)</f>
         <v>93.68</v>
       </c>
-      <c r="G12" s="57">
+      <c r="G12" s="55">
         <f t="shared" si="1"/>
         <v>3.8843135331639619E-2</v>
       </c>
@@ -5944,14 +5973,14 @@
       </c>
     </row>
     <row r="13" spans="1:71" x14ac:dyDescent="0.4">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="65">
+      <c r="B13" s="63">
         <f>SUM($K26)</f>
         <v>147.32999999999899</v>
       </c>
-      <c r="C13" s="70">
+      <c r="C13" s="68">
         <f t="shared" si="0"/>
         <v>9.2339120845829528E-2</v>
       </c>
@@ -5959,7 +5988,7 @@
         <f>SUM(K27)</f>
         <v>33.4</v>
       </c>
-      <c r="E13" s="70">
+      <c r="E13" s="68">
         <f t="shared" si="0"/>
         <v>8.9804258980425905E-2</v>
       </c>
@@ -5967,7 +5996,7 @@
         <f>SUM($K26:$K27)</f>
         <v>180.729999999999</v>
       </c>
-      <c r="G13" s="57">
+      <c r="G13" s="55">
         <f t="shared" si="1"/>
         <v>7.493723151672918E-2</v>
       </c>
@@ -6180,7 +6209,7 @@
       </c>
     </row>
     <row r="14" spans="1:71" x14ac:dyDescent="0.4">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="46" t="s">
         <v>62</v>
       </c>
       <c r="B14" s="14">
@@ -6200,7 +6229,7 @@
         <f>SUM($K28:$K29)</f>
         <v>325.3</v>
       </c>
-      <c r="G14" s="57">
+      <c r="G14" s="55">
         <f t="shared" si="1"/>
         <v>0.13488121182090487</v>
       </c>
@@ -6413,7 +6442,7 @@
       </c>
     </row>
     <row r="15" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="47" t="s">
         <v>63</v>
       </c>
       <c r="B15" s="17">
@@ -6427,7 +6456,7 @@
         <f>SUM(K30:K31)</f>
         <v>338.52</v>
       </c>
-      <c r="E15" s="71">
+      <c r="E15" s="69">
         <f t="shared" si="0"/>
         <v>0.91019574101957412</v>
       </c>
@@ -6435,7 +6464,7 @@
         <f>SUM(K30:K31)</f>
         <v>338.52</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G15" s="56">
         <f t="shared" si="1"/>
         <v>0.14036270465912301</v>
       </c>
@@ -6648,14 +6677,14 @@
       </c>
     </row>
     <row r="16" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="63">
+      <c r="B16" s="61">
         <f>SUM(B7:B15)</f>
         <v>1595.5317599999992</v>
       </c>
-      <c r="C16" s="58">
+      <c r="C16" s="56">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6663,7 +6692,7 @@
         <f>SUM(D7:D15)</f>
         <v>371.91999999999996</v>
       </c>
-      <c r="E16" s="58">
+      <c r="E16" s="56">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6671,7 +6700,7 @@
         <f>SUM(F7:F15)</f>
         <v>2411.7517599999992</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G16" s="56">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
